--- a/Materials_DetailsAvailable_Qty.xlsx
+++ b/Materials_DetailsAvailable_Qty.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johnsonandrew/Downloads/CNCEC R:L &amp; B:L Material Prediction Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johnsonandrew/Downloads/CNCEC RL and BL Material Prediction Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304E57A3-2977-FB4D-BF5F-5C9971DB53E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD39D4C-D549-844C-A0EA-2348A22A49D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11400" yWindow="2180" windowWidth="19420" windowHeight="11020" xr2:uid="{90263BA2-E30A-4598-B8D1-B7923144A5FA}"/>
+    <workbookView xWindow="2900" yWindow="3100" windowWidth="19420" windowHeight="11020" xr2:uid="{90263BA2-E30A-4598-B8D1-B7923144A5FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="76">
   <si>
     <t>Item</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>Material_Name</t>
+  </si>
+  <si>
+    <t>GI-6000027</t>
+  </si>
+  <si>
+    <t>Solvent</t>
+  </si>
+  <si>
+    <t>Toluene</t>
   </si>
 </sst>
 </file>
@@ -808,7 +817,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6" style="14" bestFit="1" customWidth="1"/>
@@ -898,7 +907,7 @@
         <v>5025</v>
       </c>
       <c r="K2" s="12">
-        <f t="shared" ref="K2:K29" si="0">I2-J2</f>
+        <f t="shared" ref="K2:K30" si="0">I2-J2</f>
         <v>0</v>
       </c>
       <c r="L2" s="13" t="s">
@@ -1934,6 +1943,27 @@
       </c>
       <c r="L29" s="19">
         <v>46188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="E30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="23">
+        <v>2000</v>
+      </c>
+      <c r="K30" s="23">
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
